--- a/docs/verification/files/geostudio/gs2_22.xlsx
+++ b/docs/verification/files/geostudio/gs2_22.xlsx
@@ -13237,14 +13237,12 @@
       <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="L11" s="3">
-        <v>3.0</v>
-      </c>
+      <c r="L11" s="3"/>
       <c r="M11" s="3">
-        <v>50000.0</v>
+        <v>100000.0</v>
       </c>
       <c r="N11" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -13365,14 +13363,12 @@
       <c r="K12" s="3">
         <v>0.0</v>
       </c>
-      <c r="L12" s="3">
-        <v>3.0</v>
-      </c>
+      <c r="L12" s="3"/>
       <c r="M12" s="3">
-        <v>50000.0</v>
+        <v>100000.0</v>
       </c>
       <c r="N12" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
@@ -13493,14 +13489,12 @@
       <c r="K13" s="3">
         <v>0.0</v>
       </c>
-      <c r="L13" s="3">
-        <v>3.0</v>
-      </c>
+      <c r="L13" s="3"/>
       <c r="M13" s="3">
-        <v>50000.0</v>
+        <v>100000.0</v>
       </c>
       <c r="N13" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
@@ -13621,14 +13615,12 @@
       <c r="K14" s="3">
         <v>0.0</v>
       </c>
-      <c r="L14" s="3">
-        <v>3.0</v>
-      </c>
+      <c r="L14" s="3"/>
       <c r="M14" s="3">
-        <v>50000.0</v>
+        <v>100000.0</v>
       </c>
       <c r="N14" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
@@ -13749,14 +13741,12 @@
       <c r="K15" s="3">
         <v>0.0</v>
       </c>
-      <c r="L15" s="3">
-        <v>3.0</v>
-      </c>
+      <c r="L15" s="3"/>
       <c r="M15" s="3">
-        <v>50000.0</v>
+        <v>100000.0</v>
       </c>
       <c r="N15" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
@@ -13877,14 +13867,12 @@
       <c r="K16" s="3">
         <v>0.0</v>
       </c>
-      <c r="L16" s="3">
-        <v>3.0</v>
-      </c>
+      <c r="L16" s="3"/>
       <c r="M16" s="3">
-        <v>50000.0</v>
+        <v>100000.0</v>
       </c>
       <c r="N16" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
